--- a/data/trans_bre/P1432-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1432-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,25</t>
+          <t>-0,68; 2,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,53</t>
+          <t>0,96; 3,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,42</t>
+          <t>0,23; 3,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 130,21</t>
+          <t>-22,35; 124,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,37; 365,13</t>
+          <t>42,34; 458,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 314,18</t>
+          <t>6,67; 318,95</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,67</t>
+          <t>-0,29; 0,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,37</t>
+          <t>-0,56; 0,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,04</t>
+          <t>0,17; 1,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,34; 412,8</t>
+          <t>-56,64; 358,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,08; 179,35</t>
+          <t>-78,09; 151,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 957,37</t>
+          <t>21,02; 987,25</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; -0,19</t>
+          <t>-2,09; -0,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,07</t>
+          <t>0,21; 2,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,21</t>
+          <t>-0,24; 1,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,96</t>
+          <t>-0,19; 0,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,6</t>
+          <t>0,43; 1,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,44</t>
+          <t>0,45; 1,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 112,56</t>
+          <t>-16,74; 103,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,67; 310,27</t>
+          <t>42,18; 326,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,08; 417,99</t>
+          <t>59,53; 391,27</t>
         </is>
       </c>
     </row>
